--- a/excel_routes/route_HMB_MED_threats.xlsx
+++ b/excel_routes/route_HMB_MED_threats.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_260726_at_14.46\reports\excel_routes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_270726_at_12.25\reports\excel_routes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D7F8ABB-E52F-4505-A4A0-0B7054741234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C4C73CC-2EC6-4389-8624-64CDEFBE0925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12972" yWindow="348" windowWidth="10068" windowHeight="10284" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -66,28 +66,28 @@
     <t>SM-489</t>
   </si>
   <si>
+    <t>flyadeal F3-776</t>
+  </si>
+  <si>
+    <t>LOW</t>
+  </si>
+  <si>
+    <t>EGP</t>
+  </si>
+  <si>
+    <t>EgyptAir MS-675</t>
+  </si>
+  <si>
+    <t>EgyptAir MS-693</t>
+  </si>
+  <si>
+    <t>10-SEP-26</t>
+  </si>
+  <si>
     <t>EgyptAir MS-677</t>
   </si>
   <si>
-    <t>LOW</t>
-  </si>
-  <si>
-    <t>EGP</t>
-  </si>
-  <si>
-    <t>EgyptAir MS-693</t>
-  </si>
-  <si>
-    <t>EgyptAir MS-675</t>
-  </si>
-  <si>
-    <t>10-SEP-26</t>
-  </si>
-  <si>
     <t>EgyptAir MS-639</t>
-  </si>
-  <si>
-    <t>MED</t>
   </si>
   <si>
     <t>22-OCT-26</t>
@@ -132,7 +132,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -149,12 +149,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFD4EDDA"/>
         <bgColor rgb="FFD4EDDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF3CD"/>
-        <bgColor rgb="FFFFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -185,7 +179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -194,9 +188,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -563,22 +554,22 @@
         <v>13</v>
       </c>
       <c r="D2" s="2">
-        <v>6615</v>
+        <v>6129</v>
       </c>
       <c r="E2" s="2">
         <v>11393</v>
       </c>
       <c r="F2" s="2">
-        <v>-4778</v>
+        <v>-5264</v>
       </c>
       <c r="G2" s="2">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H2" s="2">
         <v>30</v>
       </c>
       <c r="I2" s="2">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>14</v>
@@ -665,7 +656,7 @@
         <v>12</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D5" s="2">
         <v>6615</v>
@@ -735,28 +726,28 @@
         <v>12</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D7" s="2">
-        <v>6711</v>
+        <v>6615</v>
       </c>
       <c r="E7" s="2">
         <v>11393</v>
       </c>
       <c r="F7" s="2">
-        <v>-4682</v>
+        <v>-4778</v>
       </c>
       <c r="G7" s="2">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H7" s="2">
         <v>30</v>
       </c>
       <c r="I7" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>20</v>
+        <v>7</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>15</v>
@@ -770,7 +761,7 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8" s="2">
         <v>6711</v>
@@ -805,7 +796,7 @@
         <v>12</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D9" s="2">
         <v>6711</v>
@@ -840,7 +831,7 @@
         <v>12</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D10" s="2">
         <v>6711</v>
@@ -878,22 +869,22 @@
         <v>25</v>
       </c>
       <c r="D11" s="2">
-        <v>8191</v>
+        <v>5583</v>
       </c>
       <c r="E11" s="2">
         <v>10738</v>
       </c>
       <c r="F11" s="2">
-        <v>-2547</v>
+        <v>-5155</v>
       </c>
       <c r="G11" s="2">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H11" s="2">
         <v>30</v>
       </c>
       <c r="I11" s="2">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>14</v>
